--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-legal-authenticator.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="255">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -733,6 +733,12 @@
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.code.translation</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.addr</t>
@@ -1108,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK65"/>
+  <dimension ref="A1:AK66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.31640625" customWidth="true" bestFit="true"/>
@@ -7194,11 +7200,9 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7249,7 +7253,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7269,10 +7273,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7295,10 +7299,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -7350,7 +7354,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7370,10 +7374,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7384,7 +7388,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -7396,10 +7400,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7451,13 +7455,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -7471,10 +7475,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7497,10 +7501,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -7552,7 +7556,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7572,10 +7576,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7586,7 +7590,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -7598,9 +7602,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="L64" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7651,7 +7657,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7671,10 +7677,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7682,10 +7688,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -7697,7 +7703,7 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>95</v>
+        <v>251</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7753,7 +7759,7 @@
         <v>252</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>75</v>
@@ -7765,6 +7771,105 @@
         <v>74</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>74</v>
       </c>
     </row>
